--- a/data/summary.xlsx
+++ b/data/summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="37">
   <si>
     <t>Тип (RU)</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>Бетон В230 F150 W8</t>
+  </si>
+  <si>
+    <t>Экструдированный пенополистирол</t>
   </si>
   <si>
     <t>-</t>
@@ -516,10 +519,10 @@
         <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -536,10 +539,10 @@
         <v>367</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -556,10 +559,10 @@
         <v>486</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -576,10 +579,10 @@
         <v>381</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -599,7 +602,7 @@
         <v>0.275</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -619,7 +622,7 @@
         <v>12.655</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -639,7 +642,7 @@
         <v>8.646000000000001</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -659,7 +662,7 @@
         <v>0.066</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -679,7 +682,7 @@
         <v>94.282</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -699,7 +702,7 @@
         <v>98.71299999999999</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -719,7 +722,7 @@
         <v>35.004</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -736,10 +739,10 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -756,10 +759,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -770,16 +773,16 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D15">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>12.773</v>
+        <v>1.535</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -790,16 +793,16 @@
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>1.535</v>
+        <v>6.392</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -810,16 +813,16 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="E17">
-        <v>6.392</v>
+        <v>3115.897</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -830,16 +833,16 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E18">
-        <v>3115.897</v>
+        <v>1108.49</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -850,16 +853,16 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D19">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E19">
-        <v>1108.49</v>
+        <v>12.773</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -876,10 +879,10 @@
         <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -899,7 +902,7 @@
         <v>603.896</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -919,7 +922,7 @@
         <v>2485.343</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -939,7 +942,7 @@
         <v>1372.621</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -959,7 +962,7 @@
         <v>2926.051</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -979,7 +982,7 @@
         <v>0.128</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/summary.xlsx
+++ b/data/summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="26">
   <si>
     <t>Тип (RU)</t>
   </si>
@@ -34,24 +34,12 @@
     <t>Площадь, м²</t>
   </si>
   <si>
-    <t>IfcDiscreteAccessory</t>
-  </si>
-  <si>
-    <t>IfcElementAssembly</t>
-  </si>
-  <si>
-    <t>IfcOpeningElement</t>
-  </si>
-  <si>
     <t>Балки</t>
   </si>
   <si>
     <t>Колонны</t>
   </si>
   <si>
-    <t>Лестничные_марши</t>
-  </si>
-  <si>
     <t>Лестничные_площадки</t>
   </si>
   <si>
@@ -61,9 +49,6 @@
     <t>Перекрытия</t>
   </si>
   <si>
-    <t>Плиты</t>
-  </si>
-  <si>
     <t>Подготовка_фундамента</t>
   </si>
   <si>
@@ -73,46 +58,28 @@
     <t>Фундаментные_плиты</t>
   </si>
   <si>
-    <t>Элементы</t>
-  </si>
-  <si>
     <t>IfcBeam</t>
   </si>
   <si>
     <t>IfcColumn</t>
   </si>
   <si>
-    <t>IfcStairFlight</t>
-  </si>
-  <si>
     <t>IfcSlab</t>
   </si>
   <si>
     <t>IfcRamp</t>
   </si>
   <si>
-    <t>IfcPlate</t>
-  </si>
-  <si>
     <t>IfcWall</t>
   </si>
   <si>
-    <t>IfcMember</t>
-  </si>
-  <si>
-    <t>Бетон</t>
+    <t>Бетон В25 F100 W6</t>
+  </si>
+  <si>
+    <t>Бетон В30 F150 W8</t>
   </si>
   <si>
     <t>Бетон В30</t>
-  </si>
-  <si>
-    <t>Бетон В25</t>
-  </si>
-  <si>
-    <t>Бетон В25 F100 W6</t>
-  </si>
-  <si>
-    <t>Бетон В30 F150 W8</t>
   </si>
   <si>
     <t>Бетон В15 F150 W8</t>
@@ -482,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -510,59 +477,59 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="E2">
+        <v>12.655</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>367</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="E3">
+        <v>8.646000000000001</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>486</v>
-      </c>
-      <c r="E4" t="s">
-        <v>36</v>
+        <v>59</v>
+      </c>
+      <c r="E4">
+        <v>94.282</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -570,19 +537,19 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>381</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
+        <v>99</v>
+      </c>
+      <c r="E5">
+        <v>35.004</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -590,59 +557,59 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>46</v>
-      </c>
-      <c r="E6">
-        <v>0.275</v>
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>12.655</v>
+        <v>1.535</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>8.646000000000001</v>
+        <v>6.392</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -650,19 +617,19 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="E9">
-        <v>0.066</v>
+        <v>3115.897</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -670,319 +637,119 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D10">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E10">
-        <v>94.282</v>
+        <v>1108.49</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D11">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>98.71299999999999</v>
+        <v>12.773</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12">
-        <v>99</v>
-      </c>
       <c r="E12">
-        <v>35.004</v>
+        <v>603.896</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13" t="s">
-        <v>36</v>
+        <v>1468</v>
+      </c>
+      <c r="E13">
+        <v>2485.343</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>36</v>
+        <v>293</v>
+      </c>
+      <c r="E14">
+        <v>1372.621</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>1.535</v>
+        <v>2926.051</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>6.392</v>
-      </c>
-      <c r="F16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17">
-        <v>86</v>
-      </c>
-      <c r="E17">
-        <v>3115.897</v>
-      </c>
-      <c r="F17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18">
-        <v>77</v>
-      </c>
-      <c r="E18">
-        <v>1108.49</v>
-      </c>
-      <c r="F18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19">
-        <v>40</v>
-      </c>
-      <c r="E19">
-        <v>12.773</v>
-      </c>
-      <c r="F19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20">
-        <v>103</v>
-      </c>
-      <c r="E20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21">
-        <v>12</v>
-      </c>
-      <c r="E21">
-        <v>603.896</v>
-      </c>
-      <c r="F21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22">
-        <v>1468</v>
-      </c>
-      <c r="E22">
-        <v>2485.343</v>
-      </c>
-      <c r="F22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23">
-        <v>293</v>
-      </c>
-      <c r="E23">
-        <v>1372.621</v>
-      </c>
-      <c r="F23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24">
-        <v>11</v>
-      </c>
-      <c r="E24">
-        <v>2926.051</v>
-      </c>
-      <c r="F24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25">
-        <v>94</v>
-      </c>
-      <c r="E25">
-        <v>0.128</v>
-      </c>
-      <c r="F25" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/summary.xlsx
+++ b/data/summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="26">
   <si>
     <t>Тип (RU)</t>
   </si>
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -554,19 +554,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
+      <c r="E6">
+        <v>13.31</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -574,19 +574,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>1.535</v>
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -600,13 +600,13 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>6.392</v>
+        <v>1.535</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -620,13 +620,13 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>3115.897</v>
+        <v>6.392</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E10">
-        <v>1108.49</v>
+        <v>3115.897</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -660,13 +660,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E11">
-        <v>12.773</v>
+        <v>1095.18</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -674,19 +674,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E12">
-        <v>603.896</v>
+        <v>12.773</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -694,19 +694,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13">
-        <v>1468</v>
-      </c>
       <c r="E13">
-        <v>2485.343</v>
+        <v>603.896</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -720,13 +720,13 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14">
-        <v>293</v>
+        <v>1468</v>
       </c>
       <c r="E14">
-        <v>1372.621</v>
+        <v>2485.343</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -734,21 +734,41 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15">
+        <v>293</v>
+      </c>
+      <c r="E15">
+        <v>1372.621</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16">
         <v>11</v>
       </c>
-      <c r="E15">
+      <c r="E16">
         <v>2926.051</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F16" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/summary.xlsx
+++ b/data/summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
   <si>
     <t>Тип (RU)</t>
   </si>
@@ -40,6 +40,9 @@
     <t>Колонны</t>
   </si>
   <si>
+    <t>Лестничные_марши</t>
+  </si>
+  <si>
     <t>Лестничные_площадки</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t>IfcColumn</t>
   </si>
   <si>
+    <t>IfcStairFlight</t>
+  </si>
+  <si>
     <t>IfcSlab</t>
   </si>
   <si>
@@ -77,6 +83,9 @@
   </si>
   <si>
     <t>Бетон В30 F150 W8</t>
+  </si>
+  <si>
+    <t>Бетон</t>
   </si>
   <si>
     <t>Бетон В30</t>
@@ -449,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -477,10 +486,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>39</v>
@@ -489,7 +498,7 @@
         <v>12.655</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -497,10 +506,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>31</v>
@@ -509,7 +518,7 @@
         <v>8.646000000000001</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -517,10 +526,10 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4">
         <v>59</v>
@@ -529,7 +538,7 @@
         <v>94.282</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -537,39 +546,39 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="E5">
-        <v>35.004</v>
+        <v>98.71299999999999</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="E6">
-        <v>13.31</v>
+        <v>35.004</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -577,19 +586,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>13.31</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -597,99 +606,99 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8">
-        <v>1.535</v>
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>6.392</v>
+        <v>1.535</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>3115.897</v>
+        <v>6.392</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="E11">
-        <v>1095.18</v>
+        <v>3115.897</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D12">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E12">
-        <v>12.773</v>
+        <v>1095.18</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -697,19 +706,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E13">
-        <v>603.896</v>
+        <v>12.773</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -720,36 +729,36 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D14">
-        <v>1468</v>
+        <v>12</v>
       </c>
       <c r="E14">
-        <v>2485.343</v>
+        <v>603.896</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15">
-        <v>293</v>
+        <v>1468</v>
       </c>
       <c r="E15">
-        <v>1372.621</v>
+        <v>2485.343</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -757,19 +766,39 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16">
+        <v>293</v>
+      </c>
+      <c r="E16">
+        <v>1372.621</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17">
         <v>11</v>
       </c>
-      <c r="E16">
+      <c r="E17">
         <v>2926.051</v>
       </c>
-      <c r="F16" t="s">
-        <v>25</v>
+      <c r="F17" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/data/summary.xlsx
+++ b/data/summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
   <si>
     <t>Тип (RU)</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>Объем, м³</t>
-  </si>
-  <si>
-    <t>Площадь, м²</t>
   </si>
   <si>
     <t>Балки</t>
@@ -458,10 +455,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,19 +474,16 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>39</v>
@@ -497,19 +491,16 @@
       <c r="E2">
         <v>12.655</v>
       </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>31</v>
@@ -517,19 +508,16 @@
       <c r="E3">
         <v>8.646000000000001</v>
       </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>59</v>
@@ -537,19 +525,16 @@
       <c r="E4">
         <v>94.282</v>
       </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>125</v>
@@ -557,19 +542,16 @@
       <c r="E5">
         <v>98.71299999999999</v>
       </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>99</v>
@@ -577,19 +559,16 @@
       <c r="E6">
         <v>35.004</v>
       </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -597,39 +576,33 @@
       <c r="E7">
         <v>13.31</v>
       </c>
-      <c r="F7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -637,19 +610,16 @@
       <c r="E9">
         <v>1.535</v>
       </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -657,19 +627,16 @@
       <c r="E10">
         <v>6.392</v>
       </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>86</v>
@@ -677,19 +644,16 @@
       <c r="E11">
         <v>3115.897</v>
       </c>
-      <c r="F11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>68</v>
@@ -697,19 +661,16 @@
       <c r="E12">
         <v>1095.18</v>
       </c>
-      <c r="F12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>40</v>
@@ -717,19 +678,16 @@
       <c r="E13">
         <v>12.773</v>
       </c>
-      <c r="F13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>12</v>
@@ -737,19 +695,16 @@
       <c r="E14">
         <v>603.896</v>
       </c>
-      <c r="F14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
         <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>21</v>
       </c>
       <c r="D15">
         <v>1468</v>
@@ -757,19 +712,16 @@
       <c r="E15">
         <v>2485.343</v>
       </c>
-      <c r="F15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16">
         <v>293</v>
@@ -777,28 +729,22 @@
       <c r="E16">
         <v>1372.621</v>
       </c>
-      <c r="F16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17">
         <v>11</v>
       </c>
       <c r="E17">
         <v>2926.051</v>
-      </c>
-      <c r="F17" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/data/summary.xlsx
+++ b/data/summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
   <si>
     <t>Тип (RU)</t>
   </si>
@@ -88,13 +88,13 @@
     <t>Бетон В30</t>
   </si>
   <si>
+    <t>Бетон В230 F150 W8</t>
+  </si>
+  <si>
+    <t>Экструдированный пенополистирол</t>
+  </si>
+  <si>
     <t>Бетон В15 F150 W8</t>
-  </si>
-  <si>
-    <t>Бетон В230 F150 W8</t>
-  </si>
-  <si>
-    <t>Экструдированный пенополистирол</t>
   </si>
   <si>
     <t>-</t>
@@ -455,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -605,10 +605,10 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>1.535</v>
+        <v>6.392</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -619,13 +619,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="E10">
-        <v>6.392</v>
+        <v>3115.897</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -636,13 +636,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E11">
-        <v>3115.897</v>
+        <v>1095.18</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -653,18 +653,18 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="E12">
-        <v>1095.18</v>
+        <v>12.773</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -673,27 +673,27 @@
         <v>26</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E13">
-        <v>12.773</v>
+        <v>605.431</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>1468</v>
       </c>
       <c r="E14">
-        <v>603.896</v>
+        <v>2485.343</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -704,46 +704,29 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15">
-        <v>1468</v>
+        <v>293</v>
       </c>
       <c r="E15">
-        <v>2485.343</v>
+        <v>1372.621</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
       <c r="D16">
-        <v>293</v>
+        <v>11</v>
       </c>
       <c r="E16">
-        <v>1372.621</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17">
-        <v>11</v>
-      </c>
-      <c r="E17">
         <v>2926.051</v>
       </c>
     </row>

--- a/data/summary.xlsx
+++ b/data/summary.xlsx
@@ -88,13 +88,13 @@
     <t>Бетон В30</t>
   </si>
   <si>
+    <t>Экструдированный пенополистирол</t>
+  </si>
+  <si>
+    <t>Бетон В15 F150 W8</t>
+  </si>
+  <si>
     <t>Бетон В230 F150 W8</t>
-  </si>
-  <si>
-    <t>Экструдированный пенополистирол</t>
-  </si>
-  <si>
-    <t>Бетон В15 F150 W8</t>
   </si>
   <si>
     <t>-</t>
@@ -602,13 +602,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="E9">
-        <v>6.392</v>
+        <v>3115.897</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -619,13 +619,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E10">
-        <v>3115.897</v>
+        <v>1095.18</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -636,18 +636,18 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D11">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>1095.18</v>
+        <v>12.773</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -656,10 +656,10 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E12">
-        <v>12.773</v>
+        <v>605.431</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -673,10 +673,10 @@
         <v>26</v>
       </c>
       <c r="D13">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>605.431</v>
+        <v>6.392</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/data/summary.xlsx
+++ b/data/summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
   <si>
     <t>Тип (RU)</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Колонны</t>
   </si>
   <si>
+    <t>Лестничные_марши</t>
+  </si>
+  <si>
     <t>Лестничные_площадки</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
     <t>IfcColumn</t>
   </si>
   <si>
+    <t>IfcStair</t>
+  </si>
+  <si>
     <t>IfcSlab</t>
   </si>
   <si>
@@ -65,6 +71,9 @@
   </si>
   <si>
     <t>Бетон В30 F150 W6</t>
+  </si>
+  <si>
+    <t>Бетон</t>
   </si>
   <si>
     <t>Бетон В25 F100 W4</t>
@@ -443,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -468,10 +477,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>32</v>
@@ -485,16 +494,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>40</v>
-      </c>
-      <c r="E3">
-        <v>22.548</v>
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -502,16 +511,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>22.548</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -519,67 +528,67 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>4.17</v>
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>2242.488</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>982.649</v>
+        <v>2242.488</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>453.753</v>
+        <v>982.649</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -587,33 +596,33 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>252.964</v>
+        <v>453.753</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>13.597</v>
+        <v>252.964</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -624,30 +633,30 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>984</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>1731.541</v>
+        <v>13.597</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12">
-        <v>163</v>
+        <v>984</v>
       </c>
       <c r="E12">
-        <v>607.577</v>
+        <v>1731.541</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -655,32 +664,49 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="E13">
-        <v>1157.093</v>
+        <v>607.577</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>1157.093</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15">
         <v>1</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>693.739</v>
       </c>
     </row>
